--- a/measurements/28/Filled_2D_sections/coronal/week28_coronal_Batch_Allmarks.xlsx
+++ b/measurements/28/Filled_2D_sections/coronal/week28_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,102 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +596,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.756692444973231</v>
+        <v>1813.151927437642</v>
       </c>
       <c r="D2" t="n">
-        <v>12.68471109867096</v>
+        <v>247.6538833550044</v>
       </c>
       <c r="E2" t="n">
-        <v>10.08894510094713</v>
+        <v>196.9746424470629</v>
       </c>
       <c r="F2" t="n">
         <v>1.257288147745016</v>
@@ -525,24 +615,54 @@
         <v>0.3714956863502292</v>
       </c>
       <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8872767857142857</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21.20163690476191</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.368365575396826</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.06297637195122</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.0859375</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.07445693597561</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>21.20163690476191</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20.75334821428571</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.231026785714286</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.816220238095238</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.320684523809524</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8872767857142857</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.239678762641285</v>
+      <c r="AG2" s="2" t="n">
+        <v>1997.256235827664</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +673,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.852468768590125</v>
+        <v>1849.659863945578</v>
       </c>
       <c r="D3" t="n">
-        <v>12.89166919196524</v>
+        <v>251.6944937478928</v>
       </c>
       <c r="E3" t="n">
-        <v>10.35060173999972</v>
+        <v>202.0831768285661</v>
       </c>
       <c r="F3" t="n">
         <v>1.245499490348045</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3669055721995437</v>
+        <v>0.3669055721995438</v>
       </c>
       <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.66108630952381</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.625744047619047</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.9415015243902439</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.109470274390244</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.025485899390244</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>21.66108630952381</v>
+      </c>
+      <c r="N3" t="n">
+        <v>18.38169642857143</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.606770833333333</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.775297619047619</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>12.18851940064896</v>
+      <c r="AG3" s="2" t="n">
+        <v>237.9663311555272</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +747,70 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.917013682331945</v>
+        <v>1874.263038548753</v>
       </c>
       <c r="D4" t="n">
-        <v>12.88228439121712</v>
+        <v>251.5112666856675</v>
       </c>
       <c r="E4" t="n">
-        <v>10.34468365587839</v>
+        <v>201.9676332814353</v>
       </c>
       <c r="F4" t="n">
         <v>1.245304817407029</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3723278442875972</v>
+        <v>0.3723278442875973</v>
       </c>
       <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.690848214285714</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.72805059523809</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.25483630952381</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.8527057926829269</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.112900152439025</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9828029725609757</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>21.72805059523809</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16.64806547619047</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.850446428571428</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.356770833333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.690848214285714</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>10.07377353819405</v>
+      <c r="AG4" s="2" t="n">
+        <v>196.6784357456934</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +821,69 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.955086258179655</v>
+        <v>1888.775510204081</v>
       </c>
       <c r="D5" t="n">
-        <v>13.1868034833815</v>
+        <v>257.4566394374484</v>
       </c>
       <c r="E5" t="n">
-        <v>10.43040853884162</v>
+        <v>203.6413095678602</v>
       </c>
       <c r="F5" t="n">
         <v>1.264265290690714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3580816077606871</v>
+        <v>0.3580816077606872</v>
       </c>
       <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.17373511904762</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.221726190476192</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.8563262195121951</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.084508384146341</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9704173018292683</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>21.17373511904762</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.71875</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.406622023809524</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AG5" s="2" t="n">
         <v>1.209730294591914</v>
       </c>
     </row>
@@ -694,42 +895,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.940511600237953</v>
+        <v>1883.219954648526</v>
       </c>
       <c r="D6" t="n">
-        <v>12.98923016175991</v>
+        <v>253.5992555391221</v>
       </c>
       <c r="E6" t="n">
-        <v>10.54817504417606</v>
+        <v>205.9405603862944</v>
       </c>
       <c r="F6" t="n">
         <v>1.231419663340876</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3679721605268871</v>
+        <v>0.3679721605268872</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.415550595238095</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.76041666666666</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.405753968253967</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.8567073170731707</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9096798780487805</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.8831935975609756</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>17.76041666666666</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16.72619047619047</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.334821428571428</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.724330357142857</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.473214285714286</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.415550595238095</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AG6" s="2" t="n">
         <v>0.4477622449803118</v>
       </c>
     </row>
@@ -741,43 +972,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.988102320047591</v>
+        <v>1901.360544217687</v>
       </c>
       <c r="D7" t="n">
-        <v>12.00178426068004</v>
+        <v>234.3205498513721</v>
       </c>
       <c r="E7" t="n">
-        <v>10.69451648723788</v>
+        <v>208.797702846073</v>
       </c>
       <c r="F7" t="n">
-        <v>1.122237202121495</v>
+        <v>1.122237202121494</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4351646270796957</v>
+        <v>0.4351646270796958</v>
       </c>
       <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.032366071428571</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16.34300595238095</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.241582961309523</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.8370807926829269</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8370807926829269</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8370807926829269</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>16.34300595238095</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.937872023809524</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.044642857142857</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.47172619047619</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.032366071428571</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.269345238095238</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.783854166666667</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1</v>
+      <c r="AG7" s="2" t="n">
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1052,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.265615704937537</v>
+        <v>2007.142857142857</v>
       </c>
       <c r="D8" t="n">
-        <v>13.92544421044792</v>
+        <v>271.8777202992212</v>
       </c>
       <c r="E8" t="n">
-        <v>10.00465623053109</v>
+        <v>195.3290025960831</v>
       </c>
       <c r="F8" t="n">
         <v>1.391896322029717</v>
@@ -807,24 +1071,54 @@
         <v>0.3412250521847012</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.2890625</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15.84263392857143</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.952380952380953</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.8114519817073171</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.8114519817073171</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.8114519817073171</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>15.84263392857143</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.011532738095238</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8.958333333333332</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.510137648809524</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.494419642857143</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.2890625</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7246643409943716</v>
+      <c r="AG8" s="2" t="n">
+        <v>1.87016369047619</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1129,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.439619274241523</v>
+        <v>2073.469387755102</v>
       </c>
       <c r="D9" t="n">
-        <v>12.17670070252768</v>
+        <v>237.7355851445879</v>
       </c>
       <c r="E9" t="n">
-        <v>9.964245159451554</v>
+        <v>194.5400245416732</v>
       </c>
       <c r="F9" t="n">
         <v>1.222039452830755</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4610192980525529</v>
+        <v>0.461019298052553</v>
       </c>
       <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.263020833333333</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11.11979166666667</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.956420068027211</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5695503048780488</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5695503048780488</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5695503048780488</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>11.11979166666667</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.232886904761905</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.384672619047619</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5.045572916666666</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.263020833333333</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.781359931988743</v>
+      <c r="AG9" s="2" t="n">
+        <v>13.17224702380952</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1206,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.505056513979774</v>
+        <v>2098.412698412698</v>
       </c>
       <c r="D10" t="n">
-        <v>12.02198981366507</v>
+        <v>234.7150392191751</v>
       </c>
       <c r="E10" t="n">
-        <v>9.929752146325461</v>
+        <v>193.8665895234971</v>
       </c>
       <c r="F10" t="n">
         <v>1.210703916523621</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4786509601727988</v>
+        <v>0.478650960172799</v>
       </c>
       <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2890625</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.20833333333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.772799744897959</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.5228658536585366</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5228658536585366</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.5228658536585366</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>10.20833333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.193824404761905</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.940104166666666</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.772600446428571</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.821800595238095</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.2890625</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7530121364915572</v>
+      <c r="AG10" s="2" t="n">
+        <v>6.414814851721938</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1283,76 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.569601427721595</v>
+        <v>2123.015873015873</v>
       </c>
       <c r="D11" t="n">
-        <v>11.94708575271979</v>
+        <v>233.2526266007196</v>
       </c>
       <c r="E11" t="n">
-        <v>9.883423031830207</v>
+        <v>192.962068716685</v>
       </c>
       <c r="F11" t="n">
         <v>1.208800403892803</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4903543353936622</v>
+        <v>0.4903543353936623</v>
       </c>
       <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.707589285714286</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.934895833333332</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.356930272108843</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.508860518292683</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.508860518292683</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.508860518292683</v>
+      <c r="M11" t="n">
+        <v>9.934895833333332</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.069568452380952</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.839285714285714</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.638392857142857</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.868303571428571</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.44047619047619</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.707589285714286</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1363,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.607674003569304</v>
+        <v>2137.528344671201</v>
       </c>
       <c r="D12" t="n">
-        <v>11.93524958738467</v>
+        <v>233.0215395632244</v>
       </c>
       <c r="E12" t="n">
-        <v>9.897710483248641</v>
+        <v>193.2410141967592</v>
       </c>
       <c r="F12" t="n">
         <v>1.205859638709826</v>
@@ -987,7 +1382,54 @@
         <v>0.4946859910685548</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.475446428571429</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.713231646825397</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.475446428571429</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.911458333333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.727678571428571</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.374255952380952</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.933407738095238</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>13.17224702380952</v>
       </c>
     </row>
     <row r="13">
@@ -998,26 +1440,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.64069006543724</v>
+        <v>2150.113378684807</v>
       </c>
       <c r="D13" t="n">
-        <v>12.12445348355828</v>
+        <v>236.7155203932807</v>
       </c>
       <c r="E13" t="n">
-        <v>10.07609360392501</v>
+        <v>196.7237322671073</v>
       </c>
       <c r="F13" t="n">
         <v>1.203289088028655</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4821895101830826</v>
+        <v>0.4821895101830825</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.216703869047619</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.808035714285714</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.355282738095238</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>14.83282180059524</v>
       </c>
     </row>
     <row r="14">
@@ -1028,35 +1511,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.624330755502677</v>
+        <v>2143.877551020408</v>
       </c>
       <c r="D14" t="n">
-        <v>11.78197469943907</v>
+        <v>230.0290298461914</v>
       </c>
       <c r="E14" t="n">
-        <v>10.05588807129278</v>
+        <v>196.3292432966686</v>
       </c>
       <c r="F14" t="n">
-        <v>1.171649347716375</v>
+        <v>1.171649347716376</v>
       </c>
       <c r="G14" t="n">
         <v>0.5091485897247101</v>
       </c>
       <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.084077380952381</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11.07328869047619</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.530443948412699</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5671684451219512</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.5671684451219512</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.5671684451219512</v>
+      <c r="M14" t="n">
+        <v>11.07328869047619</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.084077380952381</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.217261904761904</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.421874999999999</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -1067,17 +1582,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.529446757882213</v>
+        <v>2107.709750566893</v>
       </c>
       <c r="D15" t="n">
-        <v>11.98648144268408</v>
+        <v>234.0217805476416</v>
       </c>
       <c r="E15" t="n">
-        <v>10.03914926982507</v>
+        <v>196.0024381251562</v>
       </c>
       <c r="F15" t="n">
         <v>1.193973823928702</v>
@@ -1086,16 +1601,54 @@
         <v>0.4836242953823434</v>
       </c>
       <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.597842261904762</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10.38318452380952</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.740017361111111</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5306783536585366</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5318216463414634</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.53125</v>
+      <c r="M15" t="n">
+        <v>10.38318452380952</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.36086309523809</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.227678571428571</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.138020833333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.732514880952381</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.597842261904762</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>6.348214285714286</v>
       </c>
     </row>
     <row r="16">
@@ -1106,35 +1659,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.495538370017846</v>
+        <v>2094.784580498866</v>
       </c>
       <c r="D16" t="n">
-        <v>11.83177054509884</v>
+        <v>231.0012344519297</v>
       </c>
       <c r="E16" t="n">
-        <v>9.933218854229626</v>
+        <v>193.9342728682927</v>
       </c>
       <c r="F16" t="n">
         <v>1.191131567594607</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4933108084856805</v>
+        <v>0.4933108084856804</v>
       </c>
       <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.032366071428571</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9.886532738095237</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.450458829365079</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.5027629573170732</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.5063833841463414</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.5045731707317074</v>
+      <c r="M16" t="n">
+        <v>9.886532738095237</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.815848214285714</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.515997023809524</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.586309523809524</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.865699404761905</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.032366071428571</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>5.379278273809524</v>
       </c>
     </row>
     <row r="17">
@@ -1145,17 +1736,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.426234384295062</v>
+        <v>2068.367346938775</v>
       </c>
       <c r="D17" t="n">
-        <v>11.75196374044186</v>
+        <v>229.4431015991029</v>
       </c>
       <c r="E17" t="n">
-        <v>9.939136915090607</v>
+        <v>194.0498159612928</v>
       </c>
       <c r="F17" t="n">
         <v>1.182392781268445</v>
@@ -1164,7 +1755,54 @@
         <v>0.4937277386037657</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9040178571428571</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9.743303571428571</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.323350694444445</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9.743303571428571</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8.677455357142856</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8.0859375</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.604910714285714</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.9244791666666666</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9040178571428571</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>3.516156462585034</v>
       </c>
     </row>
     <row r="18">
@@ -1175,26 +1813,70 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.33224271267103</v>
+        <v>2032.539682539682</v>
       </c>
       <c r="D18" t="n">
-        <v>11.67114161282051</v>
+        <v>227.8651457741147</v>
       </c>
       <c r="E18" t="n">
-        <v>10.04261595737643</v>
+        <v>196.0701210725875</v>
       </c>
       <c r="F18" t="n">
         <v>1.162161498792344</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4919184324548497</v>
+        <v>0.4919184324548496</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8872767857142857</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.304315476190476</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.216889880952381</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.304315476190476</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.2578125</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8.469122023809524</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.165922619047619</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.8872767857142857</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>3.171130952380953</v>
       </c>
     </row>
     <row r="19">
@@ -1205,17 +1887,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.185306365258775</v>
+        <v>1976.530612244898</v>
       </c>
       <c r="D19" t="n">
-        <v>11.48438905506599</v>
+        <v>224.2190244084313</v>
       </c>
       <c r="E19" t="n">
-        <v>9.864232816347261</v>
+        <v>192.5874026048751</v>
       </c>
       <c r="F19" t="n">
         <v>1.164245539301725</v>
@@ -1224,7 +1906,48 @@
         <v>0.4940472563974392</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="J19" t="n">
+        <v>9.425223214285714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.202845982142857</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9.425223214285714</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8.309151785714285</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8.219866071428571</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>7.461681547619047</v>
       </c>
     </row>
     <row r="20">
@@ -1235,26 +1958,67 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.036287923854848</v>
+        <v>1919.727891156462</v>
       </c>
       <c r="D20" t="n">
-        <v>11.38927944985832</v>
+        <v>222.3621225924719</v>
       </c>
       <c r="E20" t="n">
-        <v>9.772589933581468</v>
+        <v>190.798184417543</v>
       </c>
       <c r="F20" t="n">
-        <v>1.165431019541855</v>
+        <v>1.165431019541854</v>
       </c>
       <c r="G20" t="n">
         <v>0.4878967404372559</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9.079241071428571</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.077752976190475</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9.079241071428571</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8.056175595238095</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.842261904761904</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>4.82109375</v>
       </c>
     </row>
     <row r="21">
@@ -1265,17 +2029,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.726055919095777</v>
+        <v>1801.473922902494</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10598132959226</v>
+        <v>216.8310640539442</v>
       </c>
       <c r="E21" t="n">
-        <v>9.615427723745022</v>
+        <v>187.7297793683551</v>
       </c>
       <c r="F21" t="n">
         <v>1.155016880025666</v>
@@ -1284,7 +2048,48 @@
         <v>0.4814983928601979</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.577008928571429</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.66806175595238</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8.577008928571429</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="22">
@@ -1294,7 +2099,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>2.231079931972789</v>
       </c>
     </row>
     <row r="23">
@@ -1308,6 +2121,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>1.597413003663004</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1317,6 +2138,80 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>1.336805555555556</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>1.032366071428571</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>2.269345238095238</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>1.783854166666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/28/Filled_2D_sections/coronal/week28_coronal_Batch_Allmarks.xlsx
+++ b/measurements/28/Filled_2D_sections/coronal/week28_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2217,4 +2423,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week28_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1997.256235827664</v>
+      </c>
+      <c r="D10" t="n">
+        <v>120.0992576499275</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1801.473922902494</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2150.113378684807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>237.9663311555272</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.55903464778243</v>
+      </c>
+      <c r="E11" t="n">
+        <v>216.8310640539442</v>
+      </c>
+      <c r="F11" t="n">
+        <v>271.8777202992212</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.209730294591914</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05683764589652709</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.122237202121494</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.391896322029717</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4477622449803118</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05910586117549183</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3412250521847012</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5091485897247101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0085.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0087.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0089.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0092.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0094.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0097.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0099.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0102.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0107.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0109.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.105012502906165</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5026246899500346</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.30182058752551</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.1742858972248</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>28</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.64669696003401</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.769294279410361</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.577008928571429</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.72805059523809</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>54</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.163483796296295</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.935470221244112</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.958333333333332</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>34</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.857274159663865</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6674148342494445</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8872767857142857</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.933407738095238</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>